--- a/Shiretoko_発注計画.xlsx
+++ b/Shiretoko_発注計画.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'店舗別発注まとめ'!$A$4:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'商品別発注まとめ'!$A$4:$M$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'発注詳細データ'!$A$4:$K$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'商品別発注まとめ'!$A$4:$M$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'発注詳細データ'!$A$4:$K$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -719,19 +719,19 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>¥ 332,024</t>
+          <t>¥ 332,504</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>684 個</t>
+          <t>685 個</t>
         </is>
       </c>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>107 個</t>
+          <t>23 個</t>
         </is>
       </c>
       <c r="G6" s="6" t="n"/>
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>18</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>193916</v>
+        <v>194396</v>
       </c>
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="1" t="n"/>
@@ -958,7 +958,7 @@
         <v>103</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>79</v>
@@ -1018,7 +1018,7 @@
       <c r="D18" s="1" t="n"/>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>推定機会損失額(上代): ¥ 105,000</t>
+          <t>推定機会損失額(上代): ¥ 52,200</t>
         </is>
       </c>
       <c r="F18" s="1" t="n"/>
@@ -1205,17 +1205,9 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>24</v>
-      </c>
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="1" t="n"/>
+      <c r="D26" s="1" t="n"/>
       <c r="E26" s="1" t="n"/>
       <c r="F26" s="1" t="n"/>
       <c r="G26" s="1" t="n"/>
@@ -1229,17 +1221,9 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>22</v>
-      </c>
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="1" t="n"/>
+      <c r="D27" s="1" t="n"/>
       <c r="E27" s="1" t="n"/>
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="n"/>
@@ -1253,17 +1237,13 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>23</v>
-      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>【推奨対策】</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n"/>
+      <c r="D28" s="1" t="n"/>
       <c r="E28" s="1" t="n"/>
       <c r="F28" s="1" t="n"/>
       <c r="G28" s="1" t="n"/>
@@ -1277,17 +1257,13 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>シレトコ野帳/横顔　エゾタヌキ</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>11</v>
-      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>1. 取引先（知床財団）へ欠品アイテム（特にシレトコ野帳）の早期増産・再生産を要請する。</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n"/>
+      <c r="D29" s="1" t="n"/>
       <c r="E29" s="1" t="n"/>
       <c r="F29" s="1" t="n"/>
       <c r="G29" s="1" t="n"/>
@@ -1301,17 +1277,13 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>知床かばん（キバナ）</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>4</v>
-      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>2. 欠品カラーの代わりに、在庫のある代替カラーの展開を強化する。</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n"/>
+      <c r="D30" s="1" t="n"/>
       <c r="E30" s="1" t="n"/>
       <c r="F30" s="1" t="n"/>
       <c r="G30" s="1" t="n"/>
@@ -1341,7 +1313,11 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="n"/>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>■ 発注数の算出ロジック</t>
+        </is>
+      </c>
       <c r="C32" s="1" t="n"/>
       <c r="D32" s="1" t="n"/>
       <c r="E32" s="1" t="n"/>
@@ -1357,9 +1333,9 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>【推奨対策】</t>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>1. 7ヶ月消化モデル: 過去2年間の同期間（7月〜翌年1月）の売上実績を平均してベース目標数を算出。</t>
         </is>
       </c>
       <c r="C33" s="1" t="n"/>
@@ -1379,7 +1355,7 @@
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>1. 取引先（知床財団）へ欠品アイテム（特にシレトコ野帳）の早期増産・再生産を要請する。</t>
+          <t>2. 安全バッファ: 定番の売れ筋商品（野帳・エコバッグ）については、機会損失を防ぐため目標数に1.2倍のバッファを適用。</t>
         </is>
       </c>
       <c r="C34" s="1" t="n"/>
@@ -1399,7 +1375,7 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>2. 欠品カラーの代わりに、在庫のある代替カラーの展開を強化する。</t>
+          <t>3. 在庫引き当てとキャップ: 目標数から「店舗現在庫」を引き、さらに「取引先在庫数」を上限（キャップ）として最終発注数を確定。</t>
         </is>
       </c>
       <c r="C35" s="1" t="n"/>
@@ -1433,11 +1409,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>■ 発注数の算出ロジック</t>
-        </is>
-      </c>
+      <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="n"/>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="1" t="n"/>
@@ -1453,11 +1425,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>1. 7ヶ月消化モデル: 過去2年間の同期間（7月〜翌年1月）の売上実績を平均してベース目標数を算出。</t>
-        </is>
-      </c>
+      <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="n"/>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="1" t="n"/>
@@ -1473,11 +1441,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>2. 安全バッファ: 定番の売れ筋商品（野帳・エコバッグ）については、機会損失を防ぐため目標数に1.2倍のバッファを適用。</t>
-        </is>
-      </c>
+      <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="n"/>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="1" t="n"/>
@@ -1493,11 +1457,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>3. 在庫引き当てとキャップ: 目標数から「店舗現在庫」を引き、さらに「取引先在庫数」を上限（キャップ）として最終発注数を確定。</t>
-        </is>
-      </c>
+      <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="n"/>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="1" t="n"/>
@@ -1782,19 +1742,19 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>18</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>248020</v>
+        <v>248620</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>193916</v>
+        <v>194396</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1851,7 +1811,7 @@
         <v>103</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D9" s="23" t="n">
         <v>79</v>
@@ -1878,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1912,43 +1872,43 @@
       <c r="B2" s="19" t="inlineStr"/>
       <c r="C2" s="19" t="inlineStr"/>
       <c r="D2" s="20">
-        <f>SUBTOTAL(9, D5:D50)</f>
+        <f>SUBTOTAL(9, D5:D45)</f>
         <v/>
       </c>
       <c r="E2" s="20">
-        <f>SUBTOTAL(9, E5:E50)</f>
+        <f>SUBTOTAL(9, E5:E45)</f>
         <v/>
       </c>
       <c r="F2" s="20">
-        <f>SUBTOTAL(9, F5:F50)</f>
+        <f>SUBTOTAL(9, F5:F45)</f>
         <v/>
       </c>
       <c r="G2" s="20">
-        <f>SUBTOTAL(9, G5:G50)</f>
+        <f>SUBTOTAL(9, G5:G45)</f>
         <v/>
       </c>
       <c r="H2" s="20">
-        <f>SUBTOTAL(9, H5:H50)</f>
+        <f>SUBTOTAL(9, H5:H45)</f>
         <v/>
       </c>
       <c r="I2" s="20">
-        <f>SUBTOTAL(9, I5:I50)</f>
+        <f>SUBTOTAL(9, I5:I45)</f>
         <v/>
       </c>
       <c r="J2" s="20">
-        <f>SUBTOTAL(9, J5:J50)</f>
+        <f>SUBTOTAL(9, J5:J45)</f>
         <v/>
       </c>
       <c r="K2" s="20">
-        <f>SUBTOTAL(9, K5:K50)</f>
+        <f>SUBTOTAL(9, K5:K45)</f>
         <v/>
       </c>
       <c r="L2" s="20">
-        <f>SUBTOTAL(9, L5:L50)</f>
+        <f>SUBTOTAL(9, L5:L45)</f>
         <v/>
       </c>
       <c r="M2" s="20">
-        <f>SUBTOTAL(9, M5:M50)</f>
+        <f>SUBTOTAL(9, M5:M45)</f>
         <v/>
       </c>
     </row>
@@ -3025,34 +2985,34 @@
         <v>600</v>
       </c>
       <c r="D27" s="23" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E27" s="23" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="F27" s="23" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>100</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="K27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="23" t="n">
-        <v>21000</v>
+        <v>36000</v>
       </c>
       <c r="M27" s="23" t="n">
-        <v>16800</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -3070,34 +3030,34 @@
         <v>600</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F28" s="25" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="I28" s="25" t="n">
         <v>100</v>
       </c>
       <c r="J28" s="25" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="K28" s="25" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>23400</v>
+        <v>36600</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>18720</v>
+        <v>29280</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -3115,34 +3075,34 @@
         <v>600</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E29" s="23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F29" s="23" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I29" s="23" t="n">
         <v>100</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K29" s="23" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>17400</v>
+        <v>24000</v>
       </c>
       <c r="M29" s="23" t="n">
-        <v>13920</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -3205,450 +3165,450 @@
         <v>600</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E31" s="23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="I31" s="23" t="n">
         <v>100</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="K31" s="23" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>25200</v>
+        <v>39000</v>
       </c>
       <c r="M31" s="23" t="n">
-        <v>20160</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>SNF00952X</t>
+          <t>SNF011X</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
+          <t>知床オリジナル　エコバッグ（海）</t>
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J32" s="25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="M32" s="25" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>SNF00953X</t>
+          <t>SNF013002X</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
+          <t>知床かばん（フウロ）</t>
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E33" s="23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F33" s="23" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="M33" s="23" t="n">
-        <v>0</v>
+        <v>10560</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>SNF00954X</t>
+          <t>SNF013003X</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
+          <t>知床かばん（りす）</t>
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F34" s="25" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G34" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J34" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="M34" s="25" t="n">
-        <v>0</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>SNF00955X</t>
+          <t>SNF014X</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾタヌキ</t>
+          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
         </is>
       </c>
       <c r="C35" s="23" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E35" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F35" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M35" s="23" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>SNF011X</t>
+          <t>SNF015001X</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（海）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F36" s="25" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" s="25" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J36" s="25" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K36" s="25" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="25" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="M36" s="25" t="n">
-        <v>3200</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>SNF013001X</t>
+          <t>SNF015002X</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>知床かばん（キバナ）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="C37" s="23" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="M37" s="23" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>SNF013002X</t>
+          <t>SNF015003X</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（フウロ）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F38" s="25" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G38" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J38" s="25" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K38" s="25" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="25" t="n">
-        <v>8400</v>
+        <v>9000</v>
       </c>
       <c r="M38" s="25" t="n">
-        <v>6720</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>SNF013003X</t>
+          <t>SNF015004X</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>知床かばん（りす）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="C39" s="23" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="M39" s="23" t="n">
-        <v>2880</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>SNF014X</t>
+          <t>SNF015005X</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="25" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G40" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J40" s="25" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K40" s="25" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="25" t="n">
-        <v>1500</v>
+        <v>9000</v>
       </c>
       <c r="M40" s="25" t="n">
-        <v>1200</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>SNF015001X</t>
+          <t>SNF016001X</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="C41" s="23" t="n">
@@ -3688,12 +3648,12 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>SNF015002X</t>
+          <t>SNF016002X</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="C42" s="25" t="n">
@@ -3733,12 +3693,12 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>SNF015003X</t>
+          <t>SNF016003X</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="C43" s="23" t="n">
@@ -3778,12 +3738,12 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>SNF015004X</t>
+          <t>SNF016004X</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="C44" s="25" t="n">
@@ -3823,12 +3783,12 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>SNF015005X</t>
+          <t>SNF016005X</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="C45" s="23" t="n">
@@ -3865,233 +3825,8 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>SNF016001X</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J46" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="K46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="25" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M46" s="25" t="n">
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>SNF016002X</t>
-        </is>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="D47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="J47" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="23" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M47" s="23" t="n">
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>SNF016003X</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J48" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="K48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="25" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M48" s="25" t="n">
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>SNF016004X</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="D49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="J49" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="K49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="23" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M49" s="23" t="n">
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>SNF016005X</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J50" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="K50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="25" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M50" s="25" t="n">
-        <v>6300</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M50"/>
+  <autoFilter ref="A4:M45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -4105,7 +3840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K197"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4138,31 +3873,31 @@
       <c r="C2" s="19" t="inlineStr"/>
       <c r="D2" s="19" t="inlineStr"/>
       <c r="E2" s="20">
-        <f>SUBTOTAL(9, E5:E197)</f>
+        <f>SUBTOTAL(9, E5:E175)</f>
         <v/>
       </c>
       <c r="F2" s="20">
-        <f>SUBTOTAL(9, F5:F197)</f>
+        <f>SUBTOTAL(9, F5:F175)</f>
         <v/>
       </c>
       <c r="G2" s="20">
-        <f>SUBTOTAL(9, G5:G197)</f>
+        <f>SUBTOTAL(9, G5:G175)</f>
         <v/>
       </c>
       <c r="H2" s="20">
-        <f>SUBTOTAL(9, H5:H197)</f>
+        <f>SUBTOTAL(9, H5:H175)</f>
         <v/>
       </c>
       <c r="I2" s="20">
-        <f>SUBTOTAL(9, I5:I197)</f>
+        <f>SUBTOTAL(9, I5:I175)</f>
         <v/>
       </c>
       <c r="J2" s="20">
-        <f>SUBTOTAL(9, J5:J197)</f>
+        <f>SUBTOTAL(9, J5:J175)</f>
         <v/>
       </c>
       <c r="K2" s="20">
-        <f>SUBTOTAL(9, K5:K197)</f>
+        <f>SUBTOTAL(9, K5:K175)</f>
         <v/>
       </c>
     </row>
@@ -4698,22 +4433,22 @@
         <v>2</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="25" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>960</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -4736,25 +4471,25 @@
         <v>600</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K17" s="23" t="n">
         <v>2400</v>
-      </c>
-      <c r="K17" s="23" t="n">
-        <v>1920</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -4777,16 +4512,16 @@
         <v>600</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="25" t="n">
         <v>0</v>
@@ -4859,7 +4594,7 @@
         <v>600</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="25" t="n">
         <v>2</v>
@@ -4888,16 +4623,16 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>SNF00952X</t>
+          <t>SNF011X</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
+          <t>知床オリジナル　エコバッグ（海）</t>
         </is>
       </c>
       <c r="D21" s="23" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>0</v>
@@ -4909,16 +4644,16 @@
         <v>1</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K21" s="23" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -4929,37 +4664,37 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>SNF00953X</t>
+          <t>SNF013002X</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
+          <t>知床かばん（フウロ）</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="25" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>480</v>
+        <v>960</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -4970,60 +4705,60 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>SNF00954X</t>
+          <t>SNF014X</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
+          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
         </is>
       </c>
       <c r="D23" s="23" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E23" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K23" s="23" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>SNF00955X</t>
+          <t>SNF001010X</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾタヌキ</t>
+          <t>知床ボトル(1L)/クリア</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="25" t="n">
         <v>1</v>
@@ -5032,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="25" t="n">
         <v>0</v>
@@ -5047,165 +4782,165 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>SNF011X</t>
+          <t>SNF001011X</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（海）</t>
+          <t>知床ボトル(1L)/シーフォーム</t>
         </is>
       </c>
       <c r="D25" s="23" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="E25" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K25" s="23" t="n">
-        <v>0</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>SNF013001X</t>
+          <t>SNF001012X</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（キバナ）</t>
+          <t>知床ボトル(1L)/グレー</t>
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="25" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>SNF013002X</t>
+          <t>SNF001018X</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>知床かばん（フウロ）</t>
+          <t>知床ボトル(1L)/ブルー</t>
         </is>
       </c>
       <c r="D27" s="23" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="E27" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>1200</v>
+        <v>8400</v>
       </c>
       <c r="K27" s="23" t="n">
-        <v>960</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>SNF014X</t>
+          <t>SNF001023X</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
+          <t>知床ボトル(1L)/グロー</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="E28" s="25" t="n">
         <v>2</v>
       </c>
       <c r="F28" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="25" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>0</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -5216,12 +4951,12 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>SNF001010X</t>
+          <t>SNF001029X</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/クリア</t>
+          <t>知床ボトル(1L)/バター</t>
         </is>
       </c>
       <c r="D29" s="23" t="n">
@@ -5237,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I29" s="23" t="n">
         <v>0</v>
@@ -5257,12 +4992,12 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>SNF001011X</t>
+          <t>SNF001030X</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/シーフォーム</t>
+          <t>知床ボトル(1L)/チェリーブロッサム</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
@@ -5298,37 +5033,37 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>SNF001012X</t>
+          <t>SNF001031X</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/グレー</t>
+          <t>知床ボトル(1L)/モカ</t>
         </is>
       </c>
       <c r="D31" s="23" t="n">
         <v>2800</v>
       </c>
       <c r="E31" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>6720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -5339,37 +5074,37 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>SNF001018X</t>
+          <t>SNF001033X</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ブルー</t>
+          <t>知床ボトル(1L)/デニム</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
         <v>2800</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" s="25" t="n">
-        <v>8400</v>
+        <v>2800</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>6720</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -5380,22 +5115,22 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>SNF001023X</t>
+          <t>SNF002001X</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/グロー</t>
+          <t>知床ボトル(0.5L)/オレンジ</t>
         </is>
       </c>
       <c r="D33" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E33" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>2</v>
@@ -5407,10 +5142,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>5600</v>
+        <v>4800</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>4480</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -5421,37 +5156,37 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>SNF001029X</t>
+          <t>SNF002010X</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/バター</t>
+          <t>知床ボトル(0.5L)/クリア</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="25" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>0</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -5462,37 +5197,37 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>SNF001030X</t>
+          <t>SNF002012X</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/チェリーブロッサム</t>
+          <t>知床ボトル(0.5L)/グレー</t>
         </is>
       </c>
       <c r="D35" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E35" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>2800</v>
+        <v>4800</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>2240</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -5503,37 +5238,37 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>SNF001031X</t>
+          <t>SNF002031X</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/モカ</t>
+          <t>知床ボトル(0.5L)/シーフォーム</t>
         </is>
       </c>
       <c r="D36" s="25" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="25" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -5544,37 +5279,37 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>SNF001033X</t>
+          <t>SNF002032X</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/デニム</t>
+          <t>知床ボトル(0.5L)/ブルー</t>
         </is>
       </c>
       <c r="D37" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E37" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" s="23" t="n">
         <v>2</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>2800</v>
+        <v>7200</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>2240</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -5585,16 +5320,16 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>SNF002001X</t>
+          <t>SNF004009X</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/オレンジ</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="E38" s="25" t="n">
         <v>4</v>
@@ -5612,10 +5347,10 @@
         <v>2</v>
       </c>
       <c r="J38" s="25" t="n">
-        <v>4800</v>
+        <v>2200</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>3840</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -5626,37 +5361,37 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>SNF002010X</t>
+          <t>SNF004020X</t>
         </is>
       </c>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/クリア</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
         </is>
       </c>
       <c r="D39" s="23" t="n">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>4800</v>
+        <v>6600</v>
       </c>
       <c r="K39" s="23" t="n">
-        <v>3840</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -5667,37 +5402,37 @@
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>SNF002012X</t>
+          <t>SNF005X</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/グレー</t>
+          <t>知床オリジナル　エコバッグ（森）</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K40" s="25" t="n">
         <v>2400</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="25" t="n">
-        <v>4800</v>
-      </c>
-      <c r="K40" s="25" t="n">
-        <v>3840</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -5708,37 +5443,37 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>SNF002031X</t>
+          <t>SNF008031X</t>
         </is>
       </c>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/シーフォーム</t>
+          <t>知床エコ手袋/フキとクマ</t>
         </is>
       </c>
       <c r="D41" s="23" t="n">
-        <v>2400</v>
+        <v>560</v>
       </c>
       <c r="E41" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F41" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H41" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="K41" s="23" t="n">
-        <v>1920</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -5749,37 +5484,37 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>SNF002032X</t>
+          <t>SNF008032X</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/ブルー</t>
+          <t>知床エコ軍手/ウニとコンブ</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
-        <v>2400</v>
+        <v>560</v>
       </c>
       <c r="E42" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42" s="25" t="n">
-        <v>7200</v>
+        <v>1120</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>5760</v>
+        <v>896</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -5790,37 +5525,37 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>SNF004009X</t>
+          <t>SNF009035X</t>
         </is>
       </c>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
+          <t>シレトコ野帳/ヒグマ</t>
         </is>
       </c>
       <c r="D43" s="23" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="E43" s="23" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H43" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>2200</v>
+        <v>27000</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>1760</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -5831,37 +5566,37 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>SNF004020X</t>
+          <t>SNF009036X</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
+          <t>シレトコ野帳/エゾシカ</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="E44" s="25" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="F44" s="25" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G44" s="25" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="H44" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="J44" s="25" t="n">
-        <v>6600</v>
+        <v>25800</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>5280</v>
+        <v>20640</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -5872,37 +5607,37 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>SNF005X</t>
+          <t>SNF009037X</t>
         </is>
       </c>
       <c r="C45" s="22" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（森）</t>
+          <t>シレトコ野帳/エゾクロテン</t>
         </is>
       </c>
       <c r="D45" s="23" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E45" s="23" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H45" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>3000</v>
+        <v>22800</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>2400</v>
+        <v>18240</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -5913,37 +5648,37 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>SNF008031X</t>
+          <t>SNF009050X</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>知床エコ手袋/フキとクマ</t>
+          <t>シレトコ野帳/エゾリス</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H46" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J46" s="25" t="n">
-        <v>2800</v>
+        <v>17400</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>2240</v>
+        <v>13920</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -5954,37 +5689,37 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>SNF008032X</t>
+          <t>SNF009051X</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>知床エコ軍手/ウニとコンブ</t>
+          <t>シレトコ野帳/キタキツネ</t>
         </is>
       </c>
       <c r="D47" s="23" t="n">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="E47" s="23" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="H47" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>1120</v>
+        <v>29400</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>896</v>
+        <v>23520</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -5995,37 +5730,37 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>SNF009035X</t>
+          <t>SNF011X</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/ヒグマ</t>
+          <t>知床オリジナル　エコバッグ（海）</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E48" s="25" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G48" s="25" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H48" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J48" s="25" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>12000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -6036,37 +5771,37 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>SNF009036X</t>
+          <t>SNF013002X</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾシカ</t>
+          <t>知床かばん（フウロ）</t>
         </is>
       </c>
       <c r="D49" s="23" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E49" s="23" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H49" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>16200</v>
+        <v>4800</v>
       </c>
       <c r="K49" s="23" t="n">
-        <v>12960</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -6077,37 +5812,37 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>SNF009037X</t>
+          <t>SNF013003X</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾクロテン</t>
+          <t>知床かばん（りす）</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G50" s="25" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J50" s="25" t="n">
-        <v>16200</v>
+        <v>2400</v>
       </c>
       <c r="K50" s="25" t="n">
-        <v>12960</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -6118,309 +5853,309 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>SNF009050X</t>
+          <t>SNF014X</t>
         </is>
       </c>
       <c r="C51" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾリス</t>
+          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
         </is>
       </c>
       <c r="D51" s="23" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E51" s="23" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H51" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>17400</v>
+        <v>500</v>
       </c>
       <c r="K51" s="23" t="n">
-        <v>13920</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>SNF009051X</t>
+          <t>SNF001007X</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/キタキツネ</t>
+          <t>知床ボトル(1L)/コスモ</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E52" s="25" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F52" s="25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G52" s="25" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H52" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="J52" s="25" t="n">
-        <v>19200</v>
+        <v>2800</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>15360</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>SNF00952X</t>
+          <t>SNF001010X</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
+          <t>知床ボトル(1L)/クリア</t>
         </is>
       </c>
       <c r="D53" s="23" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E53" s="23" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F53" s="23" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H53" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="K53" s="23" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>SNF00953X</t>
+          <t>SNF001011X</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
+          <t>知床ボトル(1L)/シーフォーム</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F54" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="25" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H54" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="25" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J54" s="25" t="n">
-        <v>9600</v>
+        <v>8400</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>7680</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>SNF00954X</t>
+          <t>SNF001012X</t>
         </is>
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
+          <t>知床ボトル(1L)/グレー</t>
         </is>
       </c>
       <c r="D55" s="23" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E55" s="23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F55" s="23" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H55" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>7680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>SNF00955X</t>
+          <t>SNF001018X</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾタヌキ</t>
+          <t>知床ボトル(1L)/ブルー</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E56" s="25" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F56" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H56" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J56" s="25" t="n">
-        <v>6600</v>
+        <v>2800</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>5280</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>SNF011X</t>
+          <t>SNF001023X</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（海）</t>
+          <t>知床ボトル(1L)/グロー</t>
         </is>
       </c>
       <c r="D57" s="23" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="E57" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H57" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="K57" s="23" t="n">
-        <v>2400</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>SNF013001X</t>
+          <t>SNF001030X</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（キバナ）</t>
+          <t>知床ボトル(1L)/チェリーブロッサム</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="25" t="n">
         <v>1</v>
@@ -6432,133 +6167,133 @@
         <v>1</v>
       </c>
       <c r="J58" s="25" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>960</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>SNF013002X</t>
+          <t>SNF001031X</t>
         </is>
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>知床かばん（フウロ）</t>
+          <t>知床ボトル(1L)/モカ</t>
         </is>
       </c>
       <c r="D59" s="23" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="E59" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F59" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>3600</v>
+        <v>5600</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>2880</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>SNF013003X</t>
+          <t>SNF001032X</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（りす）</t>
+          <t>知床ボトル(1L)/コットン</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F60" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H60" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="25" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>1920</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>SNF014X</t>
+          <t>SNF001033X</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
+          <t>知床ボトル(1L)/デニム</t>
         </is>
       </c>
       <c r="D61" s="23" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="E61" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K61" s="23" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -6569,37 +6304,37 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>SNF001007X</t>
+          <t>SNF001034X</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/コスモ</t>
+          <t>知床ボトル(1L)/ジェイド</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>2800</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="25" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>2240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -6610,37 +6345,37 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>SNF001010X</t>
+          <t>SNF002001X</t>
         </is>
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/クリア</t>
+          <t>知床ボトル(0.5L)/オレンジ</t>
         </is>
       </c>
       <c r="D63" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E63" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="K63" s="23" t="n">
-        <v>0</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -6651,37 +6386,37 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>SNF001011X</t>
+          <t>SNF002010X</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/シーフォーム</t>
+          <t>知床ボトル(0.5L)/クリア</t>
         </is>
       </c>
       <c r="D64" s="25" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E64" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F64" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J64" s="25" t="n">
-        <v>8400</v>
+        <v>4800</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>6720</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -6692,37 +6427,37 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>SNF001012X</t>
+          <t>SNF002012X</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/グレー</t>
+          <t>知床ボトル(0.5L)/グレー</t>
         </is>
       </c>
       <c r="D65" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E65" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K65" s="23" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -6733,22 +6468,22 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>SNF001018X</t>
+          <t>SNF002031X</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ブルー</t>
+          <t>知床ボトル(0.5L)/シーフォーム</t>
         </is>
       </c>
       <c r="D66" s="25" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E66" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="25" t="n">
         <v>1</v>
@@ -6760,10 +6495,10 @@
         <v>1</v>
       </c>
       <c r="J66" s="25" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>2240</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -6774,22 +6509,22 @@
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>SNF001023X</t>
+          <t>SNF002032X</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/グロー</t>
+          <t>知床ボトル(0.5L)/ブルー</t>
         </is>
       </c>
       <c r="D67" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="E67" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" s="23" t="n">
         <v>1</v>
@@ -6801,10 +6536,10 @@
         <v>1</v>
       </c>
       <c r="J67" s="23" t="n">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="K67" s="23" t="n">
-        <v>2240</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -6815,37 +6550,37 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>SNF001030X</t>
+          <t>SNF004009X</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/チェリーブロッサム</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
         </is>
       </c>
       <c r="D68" s="25" t="n">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="E68" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" s="25" t="n">
-        <v>2800</v>
+        <v>2200</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>2240</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -6856,37 +6591,37 @@
       </c>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>SNF001031X</t>
+          <t>SNF004020X</t>
         </is>
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/モカ</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
         </is>
       </c>
       <c r="D69" s="23" t="n">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="E69" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G69" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>5600</v>
+        <v>1100</v>
       </c>
       <c r="K69" s="23" t="n">
-        <v>4480</v>
+        <v>880</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -6897,37 +6632,37 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>SNF001032X</t>
+          <t>SNF008031X</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/コットン</t>
+          <t>知床エコ手袋/フキとクマ</t>
         </is>
       </c>
       <c r="D70" s="25" t="n">
-        <v>2800</v>
+        <v>560</v>
       </c>
       <c r="E70" s="25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F70" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J70" s="25" t="n">
-        <v>2800</v>
+        <v>2240</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>2240</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -6938,37 +6673,37 @@
       </c>
       <c r="B71" s="22" t="inlineStr">
         <is>
-          <t>SNF001033X</t>
+          <t>SNF008032X</t>
         </is>
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/デニム</t>
+          <t>知床エコ軍手/ウニとコンブ</t>
         </is>
       </c>
       <c r="D71" s="23" t="n">
-        <v>2800</v>
+        <v>560</v>
       </c>
       <c r="E71" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" s="23" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="K71" s="23" t="n">
-        <v>0</v>
+        <v>896</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -6979,37 +6714,37 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>SNF001034X</t>
+          <t>SNF009035X</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ジェイド</t>
+          <t>シレトコ野帳/ヒグマ</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E72" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F72" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="25" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K72" s="25" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -7020,22 +6755,22 @@
       </c>
       <c r="B73" s="22" t="inlineStr">
         <is>
-          <t>SNF002001X</t>
+          <t>SNF009036X</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/オレンジ</t>
+          <t>シレトコ野帳/エゾシカ</t>
         </is>
       </c>
       <c r="D73" s="23" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="E73" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" s="23" t="n">
         <v>2</v>
@@ -7047,10 +6782,10 @@
         <v>2</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>4800</v>
+        <v>1200</v>
       </c>
       <c r="K73" s="23" t="n">
-        <v>3840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -7061,22 +6796,22 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>SNF002010X</t>
+          <t>SNF009037X</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/クリア</t>
+          <t>シレトコ野帳/エゾクロテン</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="E74" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F74" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" s="25" t="n">
         <v>2</v>
@@ -7088,10 +6823,10 @@
         <v>2</v>
       </c>
       <c r="J74" s="25" t="n">
-        <v>4800</v>
+        <v>1200</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>3840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -7102,37 +6837,37 @@
       </c>
       <c r="B75" s="22" t="inlineStr">
         <is>
-          <t>SNF002012X</t>
+          <t>SNF009050X</t>
         </is>
       </c>
       <c r="C75" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/グレー</t>
+          <t>シレトコ野帳/エゾリス</t>
         </is>
       </c>
       <c r="D75" s="23" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="E75" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="K75" s="23" t="n">
-        <v>1920</v>
+        <v>960</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -7143,31 +6878,31 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>SNF002031X</t>
+          <t>SNF009051X</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/シーフォーム</t>
+          <t>シレトコ野帳/キタキツネ</t>
         </is>
       </c>
       <c r="D76" s="25" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="E76" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G76" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J76" s="25" t="n">
         <v>2400</v>
@@ -7184,31 +6919,31 @@
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>SNF002032X</t>
+          <t>SNF013002X</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/ブルー</t>
+          <t>知床かばん（フウロ）</t>
         </is>
       </c>
       <c r="D77" s="23" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="E77" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="23" t="n">
         <v>2</v>
       </c>
       <c r="G77" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" s="23" t="n">
         <v>2400</v>
@@ -7225,37 +6960,37 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>SNF004009X</t>
+          <t>SNF013003X</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
+          <t>知床かばん（りす）</t>
         </is>
       </c>
       <c r="D78" s="25" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E78" s="25" t="n">
         <v>2</v>
       </c>
       <c r="F78" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="25" t="n">
-        <v>2200</v>
+        <v>1200</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>1760</v>
+        <v>960</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -7266,22 +7001,22 @@
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>SNF004020X</t>
+          <t>SNF014X</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
+          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
         </is>
       </c>
       <c r="D79" s="23" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E79" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="23" t="n">
         <v>1</v>
@@ -7293,74 +7028,74 @@
         <v>1</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="K79" s="23" t="n">
-        <v>880</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>SNF008031X</t>
+          <t>SNF001010X</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
         <is>
-          <t>知床エコ手袋/フキとクマ</t>
+          <t>知床ボトル(1L)/クリア</t>
         </is>
       </c>
       <c r="D80" s="25" t="n">
-        <v>560</v>
+        <v>2800</v>
       </c>
       <c r="E80" s="25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F80" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H80" s="25" t="n">
-        <v>0</v>
-      </c>
       <c r="I80" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J80" s="25" t="n">
-        <v>2240</v>
+        <v>0</v>
       </c>
       <c r="K80" s="25" t="n">
-        <v>1792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>SNF008032X</t>
+          <t>SNF001011X</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>知床エコ軍手/ウニとコンブ</t>
+          <t>知床ボトル(1L)/シーフォーム</t>
         </is>
       </c>
       <c r="D81" s="23" t="n">
-        <v>560</v>
+        <v>2800</v>
       </c>
       <c r="E81" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="23" t="n">
         <v>1</v>
@@ -7369,77 +7104,77 @@
         <v>2</v>
       </c>
       <c r="H81" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>1120</v>
+        <v>0</v>
       </c>
       <c r="K81" s="23" t="n">
-        <v>896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>SNF009035X</t>
+          <t>SNF001018X</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/ヒグマ</t>
+          <t>知床ボトル(1L)/ブルー</t>
         </is>
       </c>
       <c r="D82" s="25" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E82" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="25" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="25" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K82" s="25" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>SNF009036X</t>
+          <t>SNF001031X</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾシカ</t>
+          <t>知床ボトル(1L)/モカ</t>
         </is>
       </c>
       <c r="D83" s="23" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E83" s="23" t="n">
         <v>1</v>
@@ -7451,42 +7186,42 @@
         <v>1</v>
       </c>
       <c r="H83" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I83" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K83" s="23" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>SNF009037X</t>
+          <t>SNF001032X</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾクロテン</t>
+          <t>知床ボトル(1L)/コットン</t>
         </is>
       </c>
       <c r="D84" s="25" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E84" s="25" t="n">
         <v>3</v>
       </c>
       <c r="F84" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="25" t="n">
         <v>2</v>
@@ -7498,379 +7233,379 @@
         <v>2</v>
       </c>
       <c r="J84" s="25" t="n">
-        <v>1200</v>
+        <v>5600</v>
       </c>
       <c r="K84" s="25" t="n">
-        <v>960</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>SNF009050X</t>
+          <t>SNF001034X</t>
         </is>
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾリス</t>
+          <t>知床ボトル(1L)/ジェイド</t>
         </is>
       </c>
       <c r="D85" s="23" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E85" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" s="23" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K85" s="23" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>SNF009051X</t>
+          <t>SNF002001X</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/キタキツネ</t>
+          <t>知床ボトル(0.5L)/オレンジ</t>
         </is>
       </c>
       <c r="D86" s="25" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E86" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G86" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H86" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J86" s="25" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="K86" s="25" t="n">
-        <v>1440</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>SNF00952X</t>
+          <t>SNF002010X</t>
         </is>
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
+          <t>知床ボトル(0.5L)/クリア</t>
         </is>
       </c>
       <c r="D87" s="23" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E87" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H87" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K87" s="23" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>SNF00953X</t>
+          <t>SNF002012X</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
+          <t>知床ボトル(0.5L)/グレー</t>
         </is>
       </c>
       <c r="D88" s="25" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E88" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G88" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H88" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" s="25" t="n">
-        <v>600</v>
+        <v>4800</v>
       </c>
       <c r="K88" s="25" t="n">
-        <v>480</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>SNF00954X</t>
+          <t>SNF002032X</t>
         </is>
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
+          <t>知床ボトル(0.5L)/ブルー</t>
         </is>
       </c>
       <c r="D89" s="23" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E89" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K89" s="23" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>SNF013001X</t>
+          <t>SNF004009X</t>
         </is>
       </c>
       <c r="C90" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（キバナ）</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
         </is>
       </c>
       <c r="D90" s="25" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E90" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G90" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H90" s="25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I90" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="25" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K90" s="25" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>SNF013002X</t>
+          <t>SNF004020X</t>
         </is>
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>知床かばん（フウロ）</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
         </is>
       </c>
       <c r="D91" s="23" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E91" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I91" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="23" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K91" s="23" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>SNF013003X</t>
+          <t>SNF005X</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（りす）</t>
+          <t>知床オリジナル　エコバッグ（森）</t>
         </is>
       </c>
       <c r="D92" s="25" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E92" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G92" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H92" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J92" s="25" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="K92" s="25" t="n">
-        <v>960</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>SNF014X</t>
+          <t>SNF008031X</t>
         </is>
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
+          <t>知床エコ手袋/フキとクマ</t>
         </is>
       </c>
       <c r="D93" s="23" t="n">
-        <v>500</v>
+        <v>560</v>
       </c>
       <c r="E93" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J93" s="23" t="n">
-        <v>500</v>
+        <v>560</v>
       </c>
       <c r="K93" s="23" t="n">
-        <v>400</v>
+        <v>448</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -7881,37 +7616,37 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>SNF001010X</t>
+          <t>SNF008032X</t>
         </is>
       </c>
       <c r="C94" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/クリア</t>
+          <t>知床エコ軍手/ウニとコンブ</t>
         </is>
       </c>
       <c r="D94" s="25" t="n">
-        <v>2800</v>
+        <v>560</v>
       </c>
       <c r="E94" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G94" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I94" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" s="25" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="K94" s="25" t="n">
-        <v>0</v>
+        <v>896</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -7922,37 +7657,37 @@
       </c>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>SNF001011X</t>
+          <t>SNF009035X</t>
         </is>
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/シーフォーム</t>
+          <t>シレトコ野帳/ヒグマ</t>
         </is>
       </c>
       <c r="D95" s="23" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E95" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F95" s="23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H95" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I95" s="23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J95" s="23" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="K95" s="23" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -7963,37 +7698,37 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>SNF001018X</t>
+          <t>SNF009036X</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ブルー</t>
+          <t>シレトコ野帳/エゾシカ</t>
         </is>
       </c>
       <c r="D96" s="25" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E96" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F96" s="25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G96" s="25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H96" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" s="25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J96" s="25" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="K96" s="25" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -8004,28 +7739,28 @@
       </c>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>SNF001031X</t>
+          <t>SNF009037X</t>
         </is>
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/モカ</t>
+          <t>シレトコ野帳/エゾクロテン</t>
         </is>
       </c>
       <c r="D97" s="23" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E97" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F97" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H97" s="23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I97" s="23" t="n">
         <v>0</v>
@@ -8045,37 +7780,37 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>SNF001032X</t>
+          <t>SNF009050X</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/コットン</t>
+          <t>シレトコ野帳/エゾリス</t>
         </is>
       </c>
       <c r="D98" s="25" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E98" s="25" t="n">
         <v>3</v>
       </c>
       <c r="F98" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G98" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H98" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I98" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" s="25" t="n">
-        <v>5600</v>
+        <v>600</v>
       </c>
       <c r="K98" s="25" t="n">
-        <v>4480</v>
+        <v>480</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -8086,37 +7821,37 @@
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>SNF001034X</t>
+          <t>SNF009051X</t>
         </is>
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ジェイド</t>
+          <t>シレトコ野帳/キタキツネ</t>
         </is>
       </c>
       <c r="D99" s="23" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E99" s="23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F99" s="23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G99" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H99" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J99" s="23" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="K99" s="23" t="n">
-        <v>0</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -8127,69 +7862,69 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>SNF002001X</t>
+          <t>SNF011X</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/オレンジ</t>
+          <t>知床オリジナル　エコバッグ（海）</t>
         </is>
       </c>
       <c r="D100" s="25" t="n">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="E100" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F100" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I100" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="25" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="K100" s="25" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>SNF002010X</t>
+          <t>SNF001011X</t>
         </is>
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/クリア</t>
+          <t>知床ボトル(1L)/シーフォーム</t>
         </is>
       </c>
       <c r="D101" s="23" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="E101" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F101" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G101" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H101" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I101" s="23" t="n">
         <v>0</v>
@@ -8204,115 +7939,115 @@
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>SNF002012X</t>
+          <t>SNF001018X</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/グレー</t>
+          <t>知床ボトル(1L)/ブルー</t>
         </is>
       </c>
       <c r="D102" s="25" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="E102" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G102" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H102" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="25" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="K102" s="25" t="n">
-        <v>3840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B103" s="22" t="inlineStr">
         <is>
-          <t>SNF002032X</t>
+          <t>SNF001023X</t>
         </is>
       </c>
       <c r="C103" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/ブルー</t>
+          <t>知床ボトル(1L)/グロー</t>
         </is>
       </c>
       <c r="D103" s="23" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="E103" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F103" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I103" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" s="23" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K103" s="23" t="n">
-        <v>0</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>SNF004009X</t>
+          <t>SNF001029X</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
+          <t>知床ボトル(1L)/バター</t>
         </is>
       </c>
       <c r="D104" s="25" t="n">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="E104" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G104" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H104" s="25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I104" s="25" t="n">
         <v>0</v>
@@ -8327,33 +8062,33 @@
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B105" s="22" t="inlineStr">
         <is>
-          <t>SNF004020X</t>
+          <t>SNF001030X</t>
         </is>
       </c>
       <c r="C105" s="22" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
+          <t>知床ボトル(1L)/チェリーブロッサム</t>
         </is>
       </c>
       <c r="D105" s="23" t="n">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="E105" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G105" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I105" s="23" t="n">
         <v>0</v>
@@ -8368,468 +8103,468 @@
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>SNF005X</t>
+          <t>SNF001031X</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（森）</t>
+          <t>知床ボトル(1L)/モカ</t>
         </is>
       </c>
       <c r="D106" s="25" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="E106" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G106" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H106" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I106" s="25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J106" s="25" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="K106" s="25" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B107" s="22" t="inlineStr">
         <is>
-          <t>SNF008031X</t>
+          <t>SNF001032X</t>
         </is>
       </c>
       <c r="C107" s="22" t="inlineStr">
         <is>
-          <t>知床エコ手袋/フキとクマ</t>
+          <t>知床ボトル(1L)/コットン</t>
         </is>
       </c>
       <c r="D107" s="23" t="n">
-        <v>560</v>
+        <v>2800</v>
       </c>
       <c r="E107" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F107" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G107" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H107" s="23" t="n">
         <v>2</v>
       </c>
       <c r="I107" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="23" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="K107" s="23" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>SNF008032X</t>
+          <t>SNF001033X</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>知床エコ軍手/ウニとコンブ</t>
+          <t>知床ボトル(1L)/デニム</t>
         </is>
       </c>
       <c r="D108" s="25" t="n">
-        <v>560</v>
+        <v>2800</v>
       </c>
       <c r="E108" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G108" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H108" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I108" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" s="25" t="n">
-        <v>1120</v>
+        <v>0</v>
       </c>
       <c r="K108" s="25" t="n">
-        <v>896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B109" s="22" t="inlineStr">
         <is>
-          <t>SNF009035X</t>
+          <t>SNF001034X</t>
         </is>
       </c>
       <c r="C109" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/ヒグマ</t>
+          <t>知床ボトル(1L)/ジェイド</t>
         </is>
       </c>
       <c r="D109" s="23" t="n">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="E109" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F109" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G109" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H109" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I109" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J109" s="23" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="K109" s="23" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>SNF009036X</t>
+          <t>SNF002010X</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾシカ</t>
+          <t>知床ボトル(0.5L)/クリア</t>
         </is>
       </c>
       <c r="D110" s="25" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E110" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F110" s="25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G110" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H110" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J110" s="25" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="K110" s="25" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B111" s="22" t="inlineStr">
         <is>
-          <t>SNF009037X</t>
+          <t>SNF002032X</t>
         </is>
       </c>
       <c r="C111" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾクロテン</t>
+          <t>知床ボトル(0.5L)/ブルー</t>
         </is>
       </c>
       <c r="D111" s="23" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E111" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G111" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H111" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I111" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="23" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K111" s="23" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>SNF009050X</t>
+          <t>SNF004009X</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾリス</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
         </is>
       </c>
       <c r="D112" s="25" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="E112" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" s="25" t="n">
         <v>3</v>
       </c>
       <c r="G112" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H112" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I112" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" s="25" t="n">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="K112" s="25" t="n">
-        <v>480</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B113" s="22" t="inlineStr">
         <is>
-          <t>SNF009051X</t>
+          <t>SNF004020X</t>
         </is>
       </c>
       <c r="C113" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/キタキツネ</t>
+          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
         </is>
       </c>
       <c r="D113" s="23" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="E113" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F113" s="23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G113" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H113" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I113" s="23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J113" s="23" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="K113" s="23" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>SNF00952X</t>
+          <t>SNF005X</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
+          <t>知床オリジナル　エコバッグ（森）</t>
         </is>
       </c>
       <c r="D114" s="25" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E114" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G114" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H114" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I114" s="25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J114" s="25" t="n">
-        <v>600</v>
+        <v>3500</v>
       </c>
       <c r="K114" s="25" t="n">
-        <v>480</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B115" s="22" t="inlineStr">
         <is>
-          <t>SNF00953X</t>
+          <t>SNF008031X</t>
         </is>
       </c>
       <c r="C115" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
+          <t>知床エコ手袋/フキとクマ</t>
         </is>
       </c>
       <c r="D115" s="23" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E115" s="23" t="n">
         <v>3</v>
       </c>
       <c r="F115" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G115" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H115" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="23" t="n">
         <v>2</v>
       </c>
       <c r="J115" s="23" t="n">
-        <v>1200</v>
+        <v>1120</v>
       </c>
       <c r="K115" s="23" t="n">
-        <v>960</v>
+        <v>896</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>SNF00954X</t>
+          <t>SNF008032X</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
+          <t>知床エコ軍手/ウニとコンブ</t>
         </is>
       </c>
       <c r="D116" s="25" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E116" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G116" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H116" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I116" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J116" s="25" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="K116" s="25" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B117" s="22" t="inlineStr">
         <is>
-          <t>SNF00955X</t>
+          <t>SNF009035X</t>
         </is>
       </c>
       <c r="C117" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾタヌキ</t>
+          <t>シレトコ野帳/ヒグマ</t>
         </is>
       </c>
       <c r="D117" s="23" t="n">
@@ -8839,63 +8574,63 @@
         <v>3</v>
       </c>
       <c r="F117" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G117" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H117" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I117" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" s="23" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K117" s="23" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>SNF011X</t>
+          <t>SNF009036X</t>
         </is>
       </c>
       <c r="C118" s="24" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（海）</t>
+          <t>シレトコ野帳/エゾシカ</t>
         </is>
       </c>
       <c r="D118" s="25" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E118" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F118" s="25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G118" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H118" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I118" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="25" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K118" s="25" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -8906,28 +8641,28 @@
       </c>
       <c r="B119" s="22" t="inlineStr">
         <is>
-          <t>SNF001011X</t>
+          <t>SNF009037X</t>
         </is>
       </c>
       <c r="C119" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/シーフォーム</t>
+          <t>シレトコ野帳/エゾクロテン</t>
         </is>
       </c>
       <c r="D119" s="23" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E119" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F119" s="23" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H119" s="23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I119" s="23" t="n">
         <v>0</v>
@@ -8947,37 +8682,37 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>SNF001018X</t>
+          <t>SNF009050X</t>
         </is>
       </c>
       <c r="C120" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ブルー</t>
+          <t>シレトコ野帳/エゾリス</t>
         </is>
       </c>
       <c r="D120" s="25" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E120" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G120" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H120" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I120" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J120" s="25" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="K120" s="25" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -8988,37 +8723,37 @@
       </c>
       <c r="B121" s="22" t="inlineStr">
         <is>
-          <t>SNF001023X</t>
+          <t>SNF009051X</t>
         </is>
       </c>
       <c r="C121" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/グロー</t>
+          <t>シレトコ野帳/キタキツネ</t>
         </is>
       </c>
       <c r="D121" s="23" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E121" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F121" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G121" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H121" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J121" s="23" t="n">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="K121" s="23" t="n">
-        <v>2240</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -9029,37 +8764,37 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>SNF001029X</t>
+          <t>SNF011X</t>
         </is>
       </c>
       <c r="C122" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/バター</t>
+          <t>知床オリジナル　エコバッグ（海）</t>
         </is>
       </c>
       <c r="D122" s="25" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="E122" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F122" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I122" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J122" s="25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K122" s="25" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -9070,37 +8805,37 @@
       </c>
       <c r="B123" s="22" t="inlineStr">
         <is>
-          <t>SNF001030X</t>
+          <t>SNF013002X</t>
         </is>
       </c>
       <c r="C123" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/チェリーブロッサム</t>
+          <t>知床かばん（フウロ）</t>
         </is>
       </c>
       <c r="D123" s="23" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="E123" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F123" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G123" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H123" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I123" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J123" s="23" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="K123" s="23" t="n">
-        <v>0</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -9111,19 +8846,19 @@
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>SNF001031X</t>
+          <t>SNF013003X</t>
         </is>
       </c>
       <c r="C124" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/モカ</t>
+          <t>知床かばん（りす）</t>
         </is>
       </c>
       <c r="D124" s="25" t="n">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="E124" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="25" t="n">
         <v>1</v>
@@ -9132,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I124" s="25" t="n">
         <v>0</v>
@@ -9152,201 +8887,201 @@
       </c>
       <c r="B125" s="22" t="inlineStr">
         <is>
-          <t>SNF001032X</t>
+          <t>SNF014X</t>
         </is>
       </c>
       <c r="C125" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/コットン</t>
+          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
         </is>
       </c>
       <c r="D125" s="23" t="n">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="E125" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I125" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" s="23" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K125" s="23" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>SNF001033X</t>
+          <t>SNF015001X</t>
         </is>
       </c>
       <c r="C126" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/デニム</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D126" s="25" t="n">
-        <v>2800</v>
+        <v>300</v>
       </c>
       <c r="E126" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H126" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J126" s="25" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K126" s="25" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B127" s="22" t="inlineStr">
         <is>
-          <t>SNF001034X</t>
+          <t>SNF015001X</t>
         </is>
       </c>
       <c r="C127" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(1L)/ジェイド</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D127" s="23" t="n">
-        <v>2800</v>
+        <v>300</v>
       </c>
       <c r="E127" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H127" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I127" s="23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J127" s="23" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="K127" s="23" t="n">
-        <v>0</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>SNF002010X</t>
+          <t>SNF015001X</t>
         </is>
       </c>
       <c r="C128" s="24" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/クリア</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D128" s="25" t="n">
-        <v>2400</v>
+        <v>300</v>
       </c>
       <c r="E128" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G128" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H128" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J128" s="25" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K128" s="25" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B129" s="22" t="inlineStr">
         <is>
-          <t>SNF002032X</t>
+          <t>SNF015001X</t>
         </is>
       </c>
       <c r="C129" s="22" t="inlineStr">
         <is>
-          <t>知床ボトル(0.5L)/ブルー</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D129" s="23" t="n">
-        <v>2400</v>
+        <v>300</v>
       </c>
       <c r="E129" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F129" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H129" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J129" s="23" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="K129" s="23" t="n">
-        <v>1920</v>
+        <v>840</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -9357,201 +9092,201 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>SNF004009X</t>
+          <t>SNF015001X</t>
         </is>
       </c>
       <c r="C130" s="24" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ホワイト</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D130" s="25" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E130" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G130" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H130" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I130" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J130" s="25" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="K130" s="25" t="n">
-        <v>1760</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B131" s="22" t="inlineStr">
         <is>
-          <t>SNF004020X</t>
+          <t>SNF015002X</t>
         </is>
       </c>
       <c r="C131" s="22" t="inlineStr">
         <is>
-          <t>知床ロゴ今治ガーゼハンカチ/ネイビー</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D131" s="23" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E131" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H131" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I131" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J131" s="23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K131" s="23" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>SNF005X</t>
+          <t>SNF015002X</t>
         </is>
       </c>
       <c r="C132" s="24" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（森）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D132" s="25" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E132" s="25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F132" s="25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G132" s="25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H132" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I132" s="25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J132" s="25" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="K132" s="25" t="n">
-        <v>2800</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B133" s="22" t="inlineStr">
         <is>
-          <t>SNF008031X</t>
+          <t>SNF015002X</t>
         </is>
       </c>
       <c r="C133" s="22" t="inlineStr">
         <is>
-          <t>知床エコ手袋/フキとクマ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D133" s="23" t="n">
-        <v>560</v>
+        <v>300</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F133" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G133" s="23" t="n">
         <v>3</v>
       </c>
       <c r="H133" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J133" s="23" t="n">
-        <v>1120</v>
+        <v>900</v>
       </c>
       <c r="K133" s="23" t="n">
-        <v>896</v>
+        <v>630</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>SNF008032X</t>
+          <t>SNF015002X</t>
         </is>
       </c>
       <c r="C134" s="24" t="inlineStr">
         <is>
-          <t>知床エコ軍手/ウニとコンブ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D134" s="25" t="n">
-        <v>560</v>
+        <v>300</v>
       </c>
       <c r="E134" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H134" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I134" s="25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J134" s="25" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K134" s="25" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -9562,201 +9297,201 @@
       </c>
       <c r="B135" s="22" t="inlineStr">
         <is>
-          <t>SNF009035X</t>
+          <t>SNF015002X</t>
         </is>
       </c>
       <c r="C135" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/ヒグマ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D135" s="23" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F135" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H135" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J135" s="23" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="K135" s="23" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>SNF009036X</t>
+          <t>SNF015003X</t>
         </is>
       </c>
       <c r="C136" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾシカ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D136" s="25" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E136" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G136" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H136" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I136" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J136" s="25" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="K136" s="25" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B137" s="22" t="inlineStr">
         <is>
-          <t>SNF009037X</t>
+          <t>SNF015003X</t>
         </is>
       </c>
       <c r="C137" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾクロテン</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D137" s="23" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H137" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I137" s="23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J137" s="23" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="K137" s="23" t="n">
-        <v>0</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>SNF009050X</t>
+          <t>SNF015003X</t>
         </is>
       </c>
       <c r="C138" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾリス</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D138" s="25" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E138" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F138" s="25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G138" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H138" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" s="25" t="n">
         <v>3</v>
       </c>
       <c r="J138" s="25" t="n">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="K138" s="25" t="n">
-        <v>1440</v>
+        <v>630</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B139" s="22" t="inlineStr">
         <is>
-          <t>SNF009051X</t>
+          <t>SNF015003X</t>
         </is>
       </c>
       <c r="C139" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/キタキツネ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D139" s="23" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H139" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J139" s="23" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K139" s="23" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -9767,201 +9502,201 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>SNF00952X</t>
+          <t>SNF015003X</t>
         </is>
       </c>
       <c r="C140" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　ヒグマ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D140" s="25" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G140" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J140" s="25" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="K140" s="25" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B141" s="22" t="inlineStr">
         <is>
-          <t>SNF00953X</t>
+          <t>SNF015004X</t>
         </is>
       </c>
       <c r="C141" s="22" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　キタキツネ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D141" s="23" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E141" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G141" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H141" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I141" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J141" s="23" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K141" s="23" t="n">
-        <v>960</v>
+        <v>630</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>SNF00954X</t>
+          <t>SNF015004X</t>
         </is>
       </c>
       <c r="C142" s="24" t="inlineStr">
         <is>
-          <t>シレトコ野帳/横顔　エゾシカ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D142" s="25" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E142" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G142" s="25" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J142" s="25" t="n">
-        <v>600</v>
+        <v>4500</v>
       </c>
       <c r="K142" s="25" t="n">
-        <v>480</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B143" s="22" t="inlineStr">
         <is>
-          <t>SNF011X</t>
+          <t>SNF015004X</t>
         </is>
       </c>
       <c r="C143" s="22" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（海）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D143" s="23" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E143" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F143" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H143" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I143" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J143" s="23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K143" s="23" t="n">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
-          <t>SNF013001X</t>
+          <t>SNF015004X</t>
         </is>
       </c>
       <c r="C144" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（キバナ）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D144" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="E144" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H144" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J144" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="E144" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G144" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H144" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J144" s="25" t="n">
-        <v>2400</v>
-      </c>
       <c r="K144" s="25" t="n">
-        <v>1920</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -9972,135 +9707,135 @@
       </c>
       <c r="B145" s="22" t="inlineStr">
         <is>
-          <t>SNF013002X</t>
+          <t>SNF015004X</t>
         </is>
       </c>
       <c r="C145" s="22" t="inlineStr">
         <is>
-          <t>知床かばん（フウロ）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D145" s="23" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E145" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F145" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G145" s="23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H145" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I145" s="23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J145" s="23" t="n">
-        <v>2400</v>
+        <v>1500</v>
       </c>
       <c r="K145" s="23" t="n">
-        <v>1920</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>SNF013003X</t>
+          <t>SNF015005X</t>
         </is>
       </c>
       <c r="C146" s="24" t="inlineStr">
         <is>
-          <t>知床かばん（りす）</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D146" s="25" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E146" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H146" s="25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I146" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J146" s="25" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K146" s="25" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B147" s="22" t="inlineStr">
         <is>
-          <t>SNF014X</t>
+          <t>SNF015005X</t>
         </is>
       </c>
       <c r="C147" s="22" t="inlineStr">
         <is>
-          <t>知床財団ﾛｺﾞｽﾃｯｶｰ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D147" s="23" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E147" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G147" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H147" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I147" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J147" s="23" t="n">
-        <v>500</v>
+        <v>4500</v>
       </c>
       <c r="K147" s="23" t="n">
-        <v>400</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B148" s="24" t="inlineStr">
         <is>
-          <t>SNF015001X</t>
+          <t>SNF015005X</t>
         </is>
       </c>
       <c r="C148" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D148" s="25" t="n">
@@ -10131,17 +9866,17 @@
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B149" s="22" t="inlineStr">
         <is>
-          <t>SNF015001X</t>
+          <t>SNF015005X</t>
         </is>
       </c>
       <c r="C149" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D149" s="23" t="n">
@@ -10154,35 +9889,35 @@
         <v>0</v>
       </c>
       <c r="G149" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H149" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I149" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J149" s="23" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="K149" s="23" t="n">
-        <v>3150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>SNF015001X</t>
+          <t>SNF015005X</t>
         </is>
       </c>
       <c r="C150" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D150" s="25" t="n">
@@ -10195,35 +9930,35 @@
         <v>0</v>
       </c>
       <c r="G150" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H150" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I150" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J150" s="25" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K150" s="25" t="n">
-        <v>630</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B151" s="22" t="inlineStr">
         <is>
-          <t>SNF015001X</t>
+          <t>SNF016001X</t>
         </is>
       </c>
       <c r="C151" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D151" s="23" t="n">
@@ -10236,35 +9971,35 @@
         <v>0</v>
       </c>
       <c r="G151" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H151" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I151" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J151" s="23" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K151" s="23" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>SNF015001X</t>
+          <t>SNF016001X</t>
         </is>
       </c>
       <c r="C152" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D152" s="25" t="n">
@@ -10277,35 +10012,35 @@
         <v>0</v>
       </c>
       <c r="G152" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H152" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I152" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J152" s="25" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="K152" s="25" t="n">
-        <v>1050</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B153" s="22" t="inlineStr">
         <is>
-          <t>SNF015002X</t>
+          <t>SNF016001X</t>
         </is>
       </c>
       <c r="C153" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D153" s="23" t="n">
@@ -10336,17 +10071,17 @@
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B154" s="24" t="inlineStr">
         <is>
-          <t>SNF015002X</t>
+          <t>SNF016001X</t>
         </is>
       </c>
       <c r="C154" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D154" s="25" t="n">
@@ -10359,35 +10094,35 @@
         <v>0</v>
       </c>
       <c r="G154" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H154" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I154" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J154" s="25" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="K154" s="25" t="n">
-        <v>3150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B155" s="22" t="inlineStr">
         <is>
-          <t>SNF015002X</t>
+          <t>SNF016001X</t>
         </is>
       </c>
       <c r="C155" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
         </is>
       </c>
       <c r="D155" s="23" t="n">
@@ -10400,35 +10135,35 @@
         <v>0</v>
       </c>
       <c r="G155" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H155" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I155" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J155" s="23" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K155" s="23" t="n">
-        <v>630</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B156" s="24" t="inlineStr">
         <is>
-          <t>SNF015002X</t>
+          <t>SNF016002X</t>
         </is>
       </c>
       <c r="C156" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D156" s="25" t="n">
@@ -10441,35 +10176,35 @@
         <v>0</v>
       </c>
       <c r="G156" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H156" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I156" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J156" s="25" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K156" s="25" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B157" s="22" t="inlineStr">
         <is>
-          <t>SNF015002X</t>
+          <t>SNF016002X</t>
         </is>
       </c>
       <c r="C157" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ケイマフリ＆フレペの滝</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D157" s="23" t="n">
@@ -10482,35 +10217,35 @@
         <v>0</v>
       </c>
       <c r="G157" s="23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H157" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I157" s="23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J157" s="23" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="K157" s="23" t="n">
-        <v>1050</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>SNF015003X</t>
+          <t>SNF016002X</t>
         </is>
       </c>
       <c r="C158" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D158" s="25" t="n">
@@ -10541,17 +10276,17 @@
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B159" s="22" t="inlineStr">
         <is>
-          <t>SNF015003X</t>
+          <t>SNF016002X</t>
         </is>
       </c>
       <c r="C159" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D159" s="23" t="n">
@@ -10564,35 +10299,35 @@
         <v>0</v>
       </c>
       <c r="G159" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H159" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I159" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J159" s="23" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="K159" s="23" t="n">
-        <v>3150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>SNF015003X</t>
+          <t>SNF016002X</t>
         </is>
       </c>
       <c r="C160" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
         </is>
       </c>
       <c r="D160" s="25" t="n">
@@ -10605,35 +10340,35 @@
         <v>0</v>
       </c>
       <c r="G160" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H160" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I160" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J160" s="25" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K160" s="25" t="n">
-        <v>630</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B161" s="22" t="inlineStr">
         <is>
-          <t>SNF015003X</t>
+          <t>SNF016003X</t>
         </is>
       </c>
       <c r="C161" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D161" s="23" t="n">
@@ -10646,35 +10381,35 @@
         <v>0</v>
       </c>
       <c r="G161" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H161" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I161" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J161" s="23" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K161" s="23" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B162" s="24" t="inlineStr">
         <is>
-          <t>SNF015003X</t>
+          <t>SNF016003X</t>
         </is>
       </c>
       <c r="C162" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/エゾシカ＆知床自然センター</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D162" s="25" t="n">
@@ -10687,35 +10422,35 @@
         <v>0</v>
       </c>
       <c r="G162" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H162" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I162" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J162" s="25" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="K162" s="25" t="n">
-        <v>1050</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B163" s="22" t="inlineStr">
         <is>
-          <t>SNF015004X</t>
+          <t>SNF016003X</t>
         </is>
       </c>
       <c r="C163" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D163" s="23" t="n">
@@ -10746,17 +10481,17 @@
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>SNF015004X</t>
+          <t>SNF016003X</t>
         </is>
       </c>
       <c r="C164" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D164" s="25" t="n">
@@ -10769,35 +10504,35 @@
         <v>0</v>
       </c>
       <c r="G164" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H164" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I164" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J164" s="25" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="K164" s="25" t="n">
-        <v>3150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B165" s="22" t="inlineStr">
         <is>
-          <t>SNF015004X</t>
+          <t>SNF016003X</t>
         </is>
       </c>
       <c r="C165" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
         </is>
       </c>
       <c r="D165" s="23" t="n">
@@ -10810,35 +10545,35 @@
         <v>0</v>
       </c>
       <c r="G165" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H165" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J165" s="23" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K165" s="23" t="n">
-        <v>630</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>SNF015004X</t>
+          <t>SNF016004X</t>
         </is>
       </c>
       <c r="C166" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D166" s="25" t="n">
@@ -10851,35 +10586,35 @@
         <v>0</v>
       </c>
       <c r="G166" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H166" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J166" s="25" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K166" s="25" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B167" s="22" t="inlineStr">
         <is>
-          <t>SNF015004X</t>
+          <t>SNF016004X</t>
         </is>
       </c>
       <c r="C167" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/オジロワシ＆プユニ岬</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D167" s="23" t="n">
@@ -10892,35 +10627,35 @@
         <v>0</v>
       </c>
       <c r="G167" s="23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H167" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I167" s="23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J167" s="23" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="K167" s="23" t="n">
-        <v>1050</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B168" s="24" t="inlineStr">
         <is>
-          <t>SNF015005X</t>
+          <t>SNF016004X</t>
         </is>
       </c>
       <c r="C168" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D168" s="25" t="n">
@@ -10951,17 +10686,17 @@
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B169" s="22" t="inlineStr">
         <is>
-          <t>SNF015005X</t>
+          <t>SNF016004X</t>
         </is>
       </c>
       <c r="C169" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D169" s="23" t="n">
@@ -10974,35 +10709,35 @@
         <v>0</v>
       </c>
       <c r="G169" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H169" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J169" s="23" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="K169" s="23" t="n">
-        <v>3150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B170" s="24" t="inlineStr">
         <is>
-          <t>SNF015005X</t>
+          <t>SNF016004X</t>
         </is>
       </c>
       <c r="C170" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
         </is>
       </c>
       <c r="D170" s="25" t="n">
@@ -11015,35 +10750,35 @@
         <v>0</v>
       </c>
       <c r="G170" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H170" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I170" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J170" s="25" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K170" s="25" t="n">
-        <v>630</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
+          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
         </is>
       </c>
       <c r="B171" s="22" t="inlineStr">
         <is>
-          <t>SNF015005X</t>
+          <t>SNF016005X</t>
         </is>
       </c>
       <c r="C171" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D171" s="23" t="n">
@@ -11056,35 +10791,35 @@
         <v>0</v>
       </c>
       <c r="G171" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H171" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I171" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J171" s="23" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K171" s="23" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
+          <t>FJALLRAVEN by 3NITY TOKYO</t>
         </is>
       </c>
       <c r="B172" s="24" t="inlineStr">
         <is>
-          <t>SNF015005X</t>
+          <t>SNF016005X</t>
         </is>
       </c>
       <c r="C172" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Badges/ヒグマ＆開拓小屋コース</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D172" s="25" t="n">
@@ -11097,35 +10832,35 @@
         <v>0</v>
       </c>
       <c r="G172" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H172" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I172" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J172" s="25" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="K172" s="25" t="n">
-        <v>1050</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
+          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
         </is>
       </c>
       <c r="B173" s="22" t="inlineStr">
         <is>
-          <t>SNF016001X</t>
+          <t>SNF016005X</t>
         </is>
       </c>
       <c r="C173" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D173" s="23" t="n">
@@ -11156,17 +10891,17 @@
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="24" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
+          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
         </is>
       </c>
       <c r="B174" s="24" t="inlineStr">
         <is>
-          <t>SNF016001X</t>
+          <t>SNF016005X</t>
         </is>
       </c>
       <c r="C174" s="24" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D174" s="25" t="n">
@@ -11179,35 +10914,35 @@
         <v>0</v>
       </c>
       <c r="G174" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H174" s="25" t="n">
         <v>0</v>
       </c>
       <c r="I174" s="25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J174" s="25" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="K174" s="25" t="n">
-        <v>3150</v>
+        <v>840</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="22" t="inlineStr">
         <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
+          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
         </is>
       </c>
       <c r="B175" s="22" t="inlineStr">
         <is>
-          <t>SNF016001X</t>
+          <t>SNF016005X</t>
         </is>
       </c>
       <c r="C175" s="22" t="inlineStr">
         <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
+          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
         </is>
       </c>
       <c r="D175" s="23" t="n">
@@ -11220,925 +10955,23 @@
         <v>0</v>
       </c>
       <c r="G175" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H175" s="23" t="n">
         <v>0</v>
       </c>
       <c r="I175" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J175" s="23" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K175" s="23" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
-        </is>
-      </c>
-      <c r="B176" s="24" t="inlineStr">
-        <is>
-          <t>SNF016001X</t>
-        </is>
-      </c>
-      <c r="C176" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
-        </is>
-      </c>
-      <c r="D176" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E176" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H176" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="J176" s="25" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K176" s="25" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
-        </is>
-      </c>
-      <c r="B177" s="22" t="inlineStr">
-        <is>
-          <t>SNF016001X</t>
-        </is>
-      </c>
-      <c r="C177" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/キタキツネ＆ホロベツ</t>
-        </is>
-      </c>
-      <c r="D177" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E177" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H177" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J177" s="23" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K177" s="23" t="n">
         <v>1050</v>
       </c>
     </row>
-    <row r="178" ht="20" customHeight="1">
-      <c r="A178" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
-        </is>
-      </c>
-      <c r="B178" s="24" t="inlineStr">
-        <is>
-          <t>SNF016002X</t>
-        </is>
-      </c>
-      <c r="C178" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
-        </is>
-      </c>
-      <c r="D178" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E178" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H178" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J178" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="K178" s="25" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
-        </is>
-      </c>
-      <c r="B179" s="22" t="inlineStr">
-        <is>
-          <t>SNF016002X</t>
-        </is>
-      </c>
-      <c r="C179" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
-        </is>
-      </c>
-      <c r="D179" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E179" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H179" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="J179" s="23" t="n">
-        <v>4500</v>
-      </c>
-      <c r="K179" s="23" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
-        </is>
-      </c>
-      <c r="B180" s="24" t="inlineStr">
-        <is>
-          <t>SNF016002X</t>
-        </is>
-      </c>
-      <c r="C180" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
-        </is>
-      </c>
-      <c r="D180" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E180" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H180" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J180" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="K180" s="25" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
-        </is>
-      </c>
-      <c r="B181" s="22" t="inlineStr">
-        <is>
-          <t>SNF016002X</t>
-        </is>
-      </c>
-      <c r="C181" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
-        </is>
-      </c>
-      <c r="D181" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E181" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H181" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="J181" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K181" s="23" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
-        </is>
-      </c>
-      <c r="B182" s="24" t="inlineStr">
-        <is>
-          <t>SNF016002X</t>
-        </is>
-      </c>
-      <c r="C182" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ケイマフリ＆フレペの滝</t>
-        </is>
-      </c>
-      <c r="D182" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E182" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="H182" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J182" s="25" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K182" s="25" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
-        </is>
-      </c>
-      <c r="B183" s="22" t="inlineStr">
-        <is>
-          <t>SNF016003X</t>
-        </is>
-      </c>
-      <c r="C183" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
-        </is>
-      </c>
-      <c r="D183" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E183" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H183" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J183" s="23" t="n">
-        <v>900</v>
-      </c>
-      <c r="K183" s="23" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="184" ht="20" customHeight="1">
-      <c r="A184" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
-        </is>
-      </c>
-      <c r="B184" s="24" t="inlineStr">
-        <is>
-          <t>SNF016003X</t>
-        </is>
-      </c>
-      <c r="C184" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
-        </is>
-      </c>
-      <c r="D184" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E184" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="H184" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="J184" s="25" t="n">
-        <v>4500</v>
-      </c>
-      <c r="K184" s="25" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="185" ht="20" customHeight="1">
-      <c r="A185" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
-        </is>
-      </c>
-      <c r="B185" s="22" t="inlineStr">
-        <is>
-          <t>SNF016003X</t>
-        </is>
-      </c>
-      <c r="C185" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
-        </is>
-      </c>
-      <c r="D185" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E185" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H185" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J185" s="23" t="n">
-        <v>900</v>
-      </c>
-      <c r="K185" s="23" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
-        </is>
-      </c>
-      <c r="B186" s="24" t="inlineStr">
-        <is>
-          <t>SNF016003X</t>
-        </is>
-      </c>
-      <c r="C186" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
-        </is>
-      </c>
-      <c r="D186" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E186" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H186" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="J186" s="25" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K186" s="25" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
-        </is>
-      </c>
-      <c r="B187" s="22" t="inlineStr">
-        <is>
-          <t>SNF016003X</t>
-        </is>
-      </c>
-      <c r="C187" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/エゾシカ＆知床自然センター</t>
-        </is>
-      </c>
-      <c r="D187" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E187" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H187" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J187" s="23" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K187" s="23" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
-        </is>
-      </c>
-      <c r="B188" s="24" t="inlineStr">
-        <is>
-          <t>SNF016004X</t>
-        </is>
-      </c>
-      <c r="C188" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
-        </is>
-      </c>
-      <c r="D188" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E188" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H188" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J188" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="K188" s="25" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="189" ht="20" customHeight="1">
-      <c r="A189" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
-        </is>
-      </c>
-      <c r="B189" s="22" t="inlineStr">
-        <is>
-          <t>SNF016004X</t>
-        </is>
-      </c>
-      <c r="C189" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
-        </is>
-      </c>
-      <c r="D189" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E189" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H189" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="J189" s="23" t="n">
-        <v>4500</v>
-      </c>
-      <c r="K189" s="23" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
-        </is>
-      </c>
-      <c r="B190" s="24" t="inlineStr">
-        <is>
-          <t>SNF016004X</t>
-        </is>
-      </c>
-      <c r="C190" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
-        </is>
-      </c>
-      <c r="D190" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E190" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H190" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J190" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="K190" s="25" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="191" ht="20" customHeight="1">
-      <c r="A191" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
-        </is>
-      </c>
-      <c r="B191" s="22" t="inlineStr">
-        <is>
-          <t>SNF016004X</t>
-        </is>
-      </c>
-      <c r="C191" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
-        </is>
-      </c>
-      <c r="D191" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E191" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H191" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I191" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="J191" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K191" s="23" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="192" ht="20" customHeight="1">
-      <c r="A192" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
-        </is>
-      </c>
-      <c r="B192" s="24" t="inlineStr">
-        <is>
-          <t>SNF016004X</t>
-        </is>
-      </c>
-      <c r="C192" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/オジロワシ＆プユニ岬</t>
-        </is>
-      </c>
-      <c r="D192" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E192" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="H192" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J192" s="25" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K192" s="25" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="193" ht="20" customHeight="1">
-      <c r="A193" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY SAPPORO HUTTE</t>
-        </is>
-      </c>
-      <c r="B193" s="22" t="inlineStr">
-        <is>
-          <t>SNF016005X</t>
-        </is>
-      </c>
-      <c r="C193" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
-        </is>
-      </c>
-      <c r="D193" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E193" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H193" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J193" s="23" t="n">
-        <v>900</v>
-      </c>
-      <c r="K193" s="23" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="194" ht="20" customHeight="1">
-      <c r="A194" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY TOKYO</t>
-        </is>
-      </c>
-      <c r="B194" s="24" t="inlineStr">
-        <is>
-          <t>SNF016005X</t>
-        </is>
-      </c>
-      <c r="C194" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
-        </is>
-      </c>
-      <c r="D194" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E194" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F194" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="H194" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="J194" s="25" t="n">
-        <v>4500</v>
-      </c>
-      <c r="K194" s="25" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="195" ht="20" customHeight="1">
-      <c r="A195" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY ルクア大阪</t>
-        </is>
-      </c>
-      <c r="B195" s="22" t="inlineStr">
-        <is>
-          <t>SNF016005X</t>
-        </is>
-      </c>
-      <c r="C195" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
-        </is>
-      </c>
-      <c r="D195" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E195" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H195" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J195" s="23" t="n">
-        <v>900</v>
-      </c>
-      <c r="K195" s="23" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="196" ht="20" customHeight="1">
-      <c r="A196" s="24" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY 大丸心斎橋</t>
-        </is>
-      </c>
-      <c r="B196" s="24" t="inlineStr">
-        <is>
-          <t>SNF016005X</t>
-        </is>
-      </c>
-      <c r="C196" s="24" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
-        </is>
-      </c>
-      <c r="D196" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="E196" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H196" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="J196" s="25" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K196" s="25" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="197" ht="20" customHeight="1">
-      <c r="A197" s="22" t="inlineStr">
-        <is>
-          <t>FJALLRAVEN by 3NITY玉川高島屋S・C</t>
-        </is>
-      </c>
-      <c r="B197" s="22" t="inlineStr">
-        <is>
-          <t>SNF016005X</t>
-        </is>
-      </c>
-      <c r="C197" s="22" t="inlineStr">
-        <is>
-          <t>SHIRETOKO SCENIC SPOTS Stickers/ヒグマ＆開拓小屋コース</t>
-        </is>
-      </c>
-      <c r="D197" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="E197" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H197" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J197" s="23" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K197" s="23" t="n">
-        <v>1050</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:K197"/>
+  <autoFilter ref="A4:K175"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>

--- a/Shiretoko_発注計画.xlsx
+++ b/Shiretoko_発注計画.xlsx
@@ -234,16 +234,16 @@
     <xf numFmtId="3" fontId="12" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1407,7 +1407,11 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>4. 新商品の目標配分: 実績のない新商品（ステッカー5種・缶バッジ5種）については、各店舗への初回配分数を設定して目標数（計300点）に加算。</t>
+        </is>
+      </c>
       <c r="C36" s="1" t="n"/>
       <c r="D36" s="1" t="n"/>
       <c r="E36" s="1" t="n"/>
@@ -1423,11 +1427,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>■ 定番商品への1.2倍バッファ適用内訳</t>
-        </is>
-      </c>
+      <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="n"/>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="1" t="n"/>
@@ -1443,36 +1443,16 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>昨期7ヶ月実績</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>今期7ヶ月実績</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>2年単純平均</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>バッファ後目標数</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>バッファ上乗せ数</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>■ 定番商品への1.2倍バッファ適用内訳</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="n"/>
+      <c r="F38" s="1" t="n"/>
+      <c r="G38" s="1" t="n"/>
       <c r="H38" s="1" t="n"/>
       <c r="I38" s="1" t="n"/>
       <c r="J38" s="1" t="n"/>
@@ -1483,25 +1463,35 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>知床オリジナル　エコバッグ（森）</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="G39" s="18" t="n">
-        <v>4</v>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>昨期7ヶ月実績</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>今期7ヶ月実績</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>2年単純平均</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>バッファ後目標数</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>バッファ上乗せ数</t>
+        </is>
       </c>
       <c r="H39" s="1" t="n"/>
       <c r="I39" s="1" t="n"/>
@@ -1515,23 +1505,23 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>シレトコ野帳/ヒグマ</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>48</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="F40" s="21" t="n">
-        <v>66</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>10.5</v>
+          <t>知床オリジナル　エコバッグ（森）</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="H40" s="1" t="n"/>
       <c r="I40" s="1" t="n"/>
@@ -1545,23 +1535,23 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾシカ</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
+          <t>シレトコ野帳/ヒグマ</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n">
         <v>63</v>
       </c>
-      <c r="D41" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>67</v>
-      </c>
-      <c r="G41" s="18" t="n">
-        <v>11</v>
+      <c r="D41" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>10.5</v>
       </c>
       <c r="H41" s="1" t="n"/>
       <c r="I41" s="1" t="n"/>
@@ -1575,23 +1565,23 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾクロテン</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="n">
+          <t>シレトコ野帳/エゾシカ</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E42" s="18" t="n">
         <v>56</v>
       </c>
-      <c r="D42" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="F42" s="21" t="n">
-        <v>51</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>8</v>
+      <c r="F42" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="H42" s="1" t="n"/>
       <c r="I42" s="1" t="n"/>
@@ -1605,22 +1595,22 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>シレトコ野帳/エゾリス</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="F43" s="19" t="n">
+          <t>シレトコ野帳/エゾクロテン</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="20" t="n">
         <v>43</v>
       </c>
-      <c r="G43" s="18" t="n">
+      <c r="F43" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="G43" s="20" t="n">
         <v>8</v>
       </c>
       <c r="H43" s="1" t="n"/>
@@ -1635,23 +1625,23 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>シレトコ野帳/キタキツネ</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="F44" s="21" t="n">
-        <v>67</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>12</v>
+          <t>シレトコ野帳/エゾリス</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="H44" s="1" t="n"/>
       <c r="I44" s="1" t="n"/>
@@ -1665,23 +1655,23 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>知床オリジナル　エコバッグ（海）</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F45" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="G45" s="18" t="n">
-        <v>1.5</v>
+          <t>シレトコ野帳/キタキツネ</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="H45" s="1" t="n"/>
       <c r="I45" s="1" t="n"/>
@@ -1693,12 +1683,26 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="1" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-      <c r="G46" s="1" t="n"/>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>知床オリジナル　エコバッグ（海）</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H46" s="1" t="n"/>
       <c r="I46" s="1" t="n"/>
       <c r="J46" s="1" t="n"/>
